--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartas'!$A$5:$K$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartas'!$A$5:$K$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -575,7 +575,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>11.43 turnos</t>
+          <t>12.64 turnos</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>46.1 %</t>
+          <t>47.5 %</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>66.6 %</t>
+          <t>68.8 %</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>36% / 44% / 20%</t>
+          <t>36% / 63% / 0%</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>FALLA</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Canal fluvial trenzado</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -751,12 +751,12 @@
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Deriva árida</t>
+          <t>Sequía prolongada</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>índice 0.61, uso 53 % (coste 1)</t>
+          <t>índice 0.51, uso 45 % (coste 1)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Ambos jugadores pierden 5 cartas del mazo cada turno.</t>
+          <t>Durante 3 turnos, ambos jugadores pierden 1 carta del mazo al robar.</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr"/>
@@ -4045,22 +4045,472 @@
       </c>
       <c r="L71" s="10" t="inlineStr"/>
     </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>biomasa</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Pradera de helechos</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="7">
+        <f>IF(F72="","",F72-E72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>Pradera de helechos</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>araucarias</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Bosque de araucarias</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="7">
+        <f>IF(F73="","",F73-E73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>Bosque de araucarias</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>ginkgos</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Arboleda de ginkgos</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="7">
+        <f>IF(F74="","",F74-E74)</f>
+        <v/>
+      </c>
+      <c r="H74" s="7" t="n"/>
+      <c r="I74" s="7" t="n"/>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>Arboleda de ginkgos</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="inlineStr"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>cicadas</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Matorral de cícadas</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="7">
+        <f>IF(F75="","",F75-E75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>Matorral de cícadas</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>equisetos</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Juncal de equisetos</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="7">
+        <f>IF(F76="","",F76-E76)</f>
+        <v/>
+      </c>
+      <c r="H76" s="7" t="n"/>
+      <c r="I76" s="7" t="n"/>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>Juncal de equisetos</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L76" s="10" t="inlineStr"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>galeria</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Bosque de galería</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="7">
+        <f>IF(F77="","",F77-E77)</f>
+        <v/>
+      </c>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>Bosque de galería</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L77" s="10" t="inlineStr"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>helechal</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Helechal arborescente</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="7">
+        <f>IF(F78="","",F78-E78)</f>
+        <v/>
+      </c>
+      <c r="H78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>Helechal arborescente</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="inlineStr"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>vega</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Vega de aluvión</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="7">
+        <f>IF(F79="","",F79-E79)</f>
+        <v/>
+      </c>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>Vega de aluvión</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>+2 Biomasa al bajarla. Pierdes 2 cartas de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L79" s="10" t="inlineStr"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>humedal</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Humedal de tierras bajas</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7">
+        <f>IF(F80="","",F80-E80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="7" t="n"/>
+      <c r="I80" s="7" t="n"/>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>Humedal de tierras bajas</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>+2 Biomasa al bajarla. Pierdes 2 cartas de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>manantial</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Manantial perenne</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Legendaria</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="7">
+        <f>IF(F81="","",F81-E81)</f>
+        <v/>
+      </c>
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>Manantial perenne</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>+3 Biomasa al bajarla. Pierdes 3 cartas de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L81" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:K71"/>
+  <autoFilter ref="A5:K81"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="F6:F71" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
+    <dataValidation sqref="F6:F81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>8</formula2>
     </dataValidation>
-    <dataValidation sqref="H6:I71" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque y Vida van de 0 a 20." type="whole" operator="between">
+    <dataValidation sqref="H6:I81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque y Vida van de 0 a 20." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation sqref="D6:D71" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
+    <dataValidation sqref="D6:D81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
       <formula1>"Común,Rara,Épica,Legendaria"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4075,7 +4525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4141,40 +4591,34 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Bruma de valle</t>
+          <t>Pradera de helechos</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Bruma de valle</t>
+          <t>Pradera de helechos, Bosque de araucarias, Arboleda de ginkgos, Matorral de cícadas, Juncal de equisetos, Bosque de galería, Helechal arborescente, Vega de aluvión, Humedal de tierras bajas, Manantial perenne</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>+1 de Vida a todos los dinosaurios del campo, mientras siga en el campo.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Vida a todos los del campo</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>efectosCampo.canalVida</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -4182,26 +4626,32 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+          <t>+1 de Vida a todos los dinosaurios del campo, mientras siga en el campo.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
+          <t>Vida a todos los del campo</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>efectosCampo.canalVida</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -4209,32 +4659,26 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Vida que se quita, a dos rivales</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.competenciaVida</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Crecida estacional</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -4242,32 +4686,32 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Crecida estacional</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
+          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>cambio de carta por turno y jugador</t>
+          <t>Vida que se quita, a dos rivales</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.llanuraReciclaPorTurno</t>
+          <t>rasgos.competenciaVida</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Crecimiento acelerado</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -4275,32 +4719,32 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Crecimiento acelerado</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
+          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Ataque, y otro tanto de Vida</t>
+          <t>cambio de carta por turno y jugador</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>rasgos.crecimientoAtaque</t>
+          <t>efectosCampo.llanuraReciclaPorTurno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Estación de lluvias</t>
+          <t>Crecimiento acelerado</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -4308,32 +4752,32 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Estación de lluvias</t>
+          <t>Crecimiento acelerado</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
+          <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>heridas que curan los saurópodos</t>
+          <t>Ataque, y otro tanto de Vida</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.bosqueCura</t>
+          <t>rasgos.crecimientoAtaque</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Fractura consolidada</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -4341,32 +4785,32 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Fractura consolidada</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>−2 Poder permanente a un dinosaurio rival.</t>
+          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Ataque que se quita</t>
+          <t>heridas que curan los saurópodos</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>rasgos.fracturaAtaque</t>
+          <t>efectosCampo.bosqueCura</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Gastrolitos</t>
+          <t>Fractura consolidada</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -4374,32 +4818,32 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Gastrolitos</t>
+          <t>Fractura consolidada</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Cura +1 de vida a un dinosaurio al final del turno</t>
+          <t>−2 Poder permanente a un dinosaurio rival.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>heridas curadas a un dinosaurio</t>
+          <t>Ataque que se quita</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>rasgos.gastrolitosCura</t>
+          <t>rasgos.fracturaAtaque</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Gregarismo</t>
+          <t>Gastrolitos</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -4407,12 +4851,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Gregarismo</t>
+          <t>Gastrolitos</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
+          <t>Cura +1 de vida a un dinosaurio al final del turno</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -4420,19 +4864,19 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Ataque a toda la especie</t>
+          <t>heridas curadas a un dinosaurio</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>rasgos.gregarismoAtaque</t>
+          <t>rasgos.gastrolitosCura</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Lago efímero</t>
+          <t>Gregarismo</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -4440,26 +4884,32 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Lago efímero</t>
+          <t>Gregarismo</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
+          <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
+          <t>Ataque a toda la especie</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.gregarismoAtaque</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Monzón de verano</t>
+          <t>Lago efímero</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -4467,32 +4917,26 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Monzón de verano</t>
+          <t>Lago efímero</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Biomasa por turno a los DOS</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>efectosCampo.sabanaBiomasa</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Mortandad estacional</t>
+          <t>Monzón de verano</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -4500,32 +4944,32 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mortandad estacional</t>
+          <t>Monzón de verano</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
+          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>de daño a TODOS, incluidos los tuyos</t>
+          <t>Biomasa por turno a los DOS</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>rasgos.mortandadDano</t>
+          <t>efectosCampo.sabanaBiomasa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Neumaticidad ósea</t>
+          <t>Mortandad estacional</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -4533,32 +4977,32 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Neumaticidad ósea</t>
+          <t>Mortandad estacional</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
+          <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Ataque permanente</t>
+          <t>de daño a TODOS, incluidos los tuyos</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>rasgos.neumaticidadAtaque</t>
+          <t>rasgos.mortandadDano</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Rebrote tras incendio</t>
+          <t>Neumaticidad ósea</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -4566,26 +5010,32 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Rebrote tras incendio</t>
+          <t>Neumaticidad ósea</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
+          <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
+          <t>Ataque permanente</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.neumaticidadAtaque</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Sequía prolongada</t>
+          <t>Rebrote tras incendio</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -4593,56 +5043,83 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Sequía prolongada</t>
+          <t>Rebrote tras incendio</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Ambos jugadores pierden 5 cartas del mazo cada turno.</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>5</v>
-      </c>
+          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>cartas de mazo que pierden los DOS</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>efectosCampo.aridezMazo</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Sequía prolongada</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Sequía prolongada</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Durante 3 turnos, ambos jugadores pierden 1 carta del mazo al robar.</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>cartas de mazo que pierden los DOS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>efectosCampo.aridezMazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>cartas que pierde el rival</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>rasgos.trampaMazoRival</t>
         </is>
@@ -5359,7 +5836,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -5479,7 +5956,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -5935,7 +6412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5995,7 +6472,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6065,7 +6542,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6236,6 +6713,16 @@
       </c>
       <c r="B31" s="4" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>biomasa</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartas'!$A$5:$K$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartas'!$A$5:$K$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1973,22 +1973,22 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>rebrote</t>
+          <t>sabana_helechos</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Rebrote tras incendio</t>
+          <t>Sabana de helechos</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Evento</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Rara</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
@@ -2005,12 +2005,12 @@
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>Rebrote tras incendio</t>
+          <t>Sabana de helechos</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
+          <t>Robas 2 cartas. Luego descartas 1 carta de tu mano al azar.</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr"/>
@@ -2018,29 +2018,29 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>carrona</t>
+          <t>inundacion</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Llanura de inundación</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Evento</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",F30-E30)</f>
@@ -2050,12 +2050,12 @@
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Llanura de inundación</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
+          <t>Ambos jugadores pierden 3 cartas del mazo. Tú robas 1.</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr"/>
@@ -2063,29 +2063,29 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>lago</t>
+          <t>canal_trenzado</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Lago efímero</t>
+          <t>Canal fluvial trenzado</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Evento</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="7">
         <f>IF(F31="","",F31-E31)</f>
@@ -2095,12 +2095,12 @@
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>Lago efímero</t>
+          <t>Canal fluvial trenzado</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
+          <t>Todos tus dinosaurios recuperan 2 de Vida.</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr"/>
@@ -2108,17 +2108,17 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>llanura</t>
+          <t>bosque_ribereno</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Crecida estacional</t>
+          <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Evento</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="7">
         <f>IF(F32="","",F32-E32)</f>
@@ -2140,12 +2140,12 @@
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Crecida estacional</t>
+          <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
+          <t>Tu rival descarta 2 cartas de su mano al azar.</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr"/>
@@ -2153,29 +2153,29 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>canal</t>
+          <t>deriva_arida</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Bruma de valle</t>
+          <t>Deriva árida</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Evento</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",F33-E33)</f>
@@ -2185,12 +2185,12 @@
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Bruma de valle</t>
+          <t>Deriva árida</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>+1 de Vida a todos los dinosaurios del campo, mientras siga en el campo.</t>
+          <t>Ambos jugadores descartan la mano entera y roban otras tantas cartas.</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr"/>
@@ -2198,22 +2198,22 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>bosque</t>
+          <t>nido</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Estación de lluvias</t>
+          <t>Nido con huevos</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Evento</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2230,12 +2230,12 @@
       <c r="I34" s="7" t="n"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>Estación de lluvias</t>
+          <t>Nido con huevos</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
+          <t>Robas 2 cartas.</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr"/>
@@ -2243,29 +2243,29 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>aridez</t>
+          <t>rebrote</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sequía prolongada</t>
+          <t>Rebrote tras incendio</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="7">
         <f>IF(F35="","",F35-E35)</f>
@@ -2275,12 +2275,12 @@
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>Sequía prolongada</t>
+          <t>Rebrote tras incendio</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Durante 3 turnos, ambos jugadores pierden 1 carta del mazo al robar.</t>
+          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr"/>
@@ -2288,29 +2288,29 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>sabana</t>
+          <t>carrona</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Monzón de verano</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",F36-E36)</f>
@@ -2320,12 +2320,12 @@
       <c r="I36" s="7" t="n"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Monzón de verano</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
+          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr"/>
@@ -2333,17 +2333,17 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>plesiopleurodon</t>
+          <t>lago</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Plesiopleurodon wellesi</t>
+          <t>Lago efímero</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Reptil marino</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -2352,29 +2352,25 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",F37-E37)</f>
         <v/>
       </c>
-      <c r="H37" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>4</v>
-      </c>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>Sigue a los grandes</t>
+          <t>Lago efímero</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>Gana +2 de Ataque si tienes en juego algún dinosaurio con más de 6 de Vida.</t>
+          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr"/>
@@ -2382,48 +2378,44 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ojoraptorsaurus</t>
+          <t>insectos</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Ojoraptorsaurus boerei</t>
+          <t>Nube de insectos</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Rara</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="7">
         <f>IF(F38="","",F38-E38)</f>
         <v/>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>4</v>
-      </c>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>Salto de entrada</t>
+          <t>Nube de insectos</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego hiere en 2 al dinosaurio de enfrente.</t>
+          <t>+1 Biomasa ahora mismo. Robas 1 carta.</t>
         </is>
       </c>
       <c r="L38" s="10" t="inlineStr"/>
@@ -2431,48 +2423,44 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>dromaeosaurus</t>
+          <t>manada_paso</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Dromaeosaurus albertensis</t>
+          <t>Manada de paso</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="7">
         <f>IF(F39="","",F39-E39)</f>
         <v/>
       </c>
-      <c r="H39" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>Jauría</t>
+          <t>Manada de paso</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>Gana +1 de Ataque por cada Dromaeosaurus en juego, sea de quien sea y este incluido.</t>
+          <t>+2 Biomasa ahora mismo. Pierdes 3 cartas de tu mazo.</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr"/>
@@ -2480,48 +2468,44 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>athenar</t>
+          <t>frutos</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Athenar bermani</t>
+          <t>Frutos de cícada</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Saurópodo</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="7">
         <f>IF(F40="","",F40-E40)</f>
         <v/>
       </c>
-      <c r="H40" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>Olfato de tormenta</t>
+          <t>Frutos de cícada</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>Al jugarlo, puedes llevarte a la mano una carta de evento de tu mazo.</t>
+          <t>+3 Biomasa ahora mismo. Tu rival roba 1 carta.</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr"/>
@@ -2529,48 +2513,44 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>sanjuansaurus</t>
+          <t>llanura</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Sanjuansaurus gordilloi</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Rara</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="7">
         <f>IF(F41="","",F41-E41)</f>
         <v/>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Olfato de tormenta</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>Al jugarlo, puedes llevarte a la mano una carta de clima de tu mazo.</t>
+          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr"/>
@@ -2578,48 +2558,44 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>suchomimus</t>
+          <t>canal</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Suchomimus tenerensis</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="7">
         <f>IF(F42="","",F42-E42)</f>
         <v/>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I42" s="8" t="n">
-        <v>7</v>
-      </c>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>Rastreo de orilla</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego descarta 1 carta del mazo de tu rival.</t>
+          <t>+1 de Vida a todos los dinosaurios del campo, mientras siga en el campo.</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr"/>
@@ -2627,48 +2603,44 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>eosinopteryx</t>
+          <t>bosque</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Eosinopteryx brevipenna</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",F43-E43)</f>
         <v/>
       </c>
-      <c r="H43" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>Percha compartida</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>Gana +1 de Vida por cada Eosinopteryx que tengas en juego, este incluido.</t>
+          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr"/>
@@ -2676,22 +2648,22 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>troodon</t>
+          <t>aridez</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Troodon formosus</t>
+          <t>Sequía prolongada</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2704,20 +2676,16 @@
         <f>IF(F44="","",F44-E44)</f>
         <v/>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="8" t="n">
-        <v>2</v>
-      </c>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>Caza coordinada</t>
+          <t>Sequía prolongada</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>Gana +1 de Ataque por cada Troodon que tengas en juego, este incluido.</t>
+          <t>Durante 3 turnos, ambos jugadores pierden 1 carta del mazo al robar.</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr"/>
@@ -2725,48 +2693,44 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>carnotaurus</t>
+          <t>sabana</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Carnotaurus sastrei</t>
+          <t>Monzón de verano</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",F45-E45)</f>
         <v/>
       </c>
-      <c r="H45" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I45" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>Territorio exclusivo</t>
+          <t>Monzón de verano</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>Para jugarlo tienes que descartar 2 cartas de tu mano.</t>
+          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr"/>
@@ -2774,48 +2738,48 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>spinosaurus</t>
+          <t>plesiopleurodon</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Spinosaurus aegyptiacus</t>
+          <t>Plesiopleurodon wellesi</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Reptil marino</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",F46-E46)</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>Draga el río</t>
+          <t>Sigue a los grandes</t>
         </is>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
+          <t>Gana +2 de Ataque si tienes en juego algún dinosaurio con más de 6 de Vida.</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr"/>
@@ -2823,48 +2787,48 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>mosasaurus</t>
+          <t>ojoraptorsaurus</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Mosasaurus hoffmannii</t>
+          <t>Ojoraptorsaurus boerei</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Reptil marino</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G47" s="7">
         <f>IF(F47="","",F47-E47)</f>
         <v/>
       </c>
       <c r="H47" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>Draga el río</t>
+          <t>Salto de entrada</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
+          <t>Cuando entra en juego hiere en 2 al dinosaurio de enfrente.</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr"/>
@@ -2872,12 +2836,12 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>halszkaraptor</t>
+          <t>dromaeosaurus</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Halszkaraptor escuilliei</t>
+          <t>Dromaeosaurus albertensis</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -2887,33 +2851,33 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Rara</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="7">
         <f>IF(F48="","",F48-E48)</f>
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>Nadador de temporal</t>
+          <t>Jauría</t>
         </is>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>Gana +2 de Vida mientras haya un clima en el campo.</t>
+          <t>Gana +1 de Ataque por cada Dromaeosaurus en juego, sea de quien sea y este incluido.</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr"/>
@@ -2921,17 +2885,17 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>tongtianlong</t>
+          <t>athenar</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Tongtianlong limosus</t>
+          <t>Athenar bermani</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Saurópodo</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -2940,29 +2904,29 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" s="7">
         <f>IF(F49="","",F49-E49)</f>
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>Nadador de temporal</t>
+          <t>Olfato de tormenta</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>Gana +2 de Ataque mientras haya un clima en el campo.</t>
+          <t>Al jugarlo, puedes llevarte a la mano una carta de evento de tu mazo.</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr"/>
@@ -2970,17 +2934,17 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>scanisaurus</t>
+          <t>sanjuansaurus</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Scanisaurus nazarowi</t>
+          <t>Sanjuansaurus gordilloi</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Reptil marino</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -2989,10 +2953,10 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50" s="7">
         <f>IF(F50="","",F50-E50)</f>
@@ -3006,12 +2970,12 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>Banco de caza</t>
+          <t>Olfato de tormenta</t>
         </is>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en juego, tus reptiles marinos ganan +1 de Ataque.</t>
+          <t>Al jugarlo, puedes llevarte a la mano una carta de clima de tu mazo.</t>
         </is>
       </c>
       <c r="L50" s="10" t="inlineStr"/>
@@ -3019,12 +2983,12 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>monolophosaurus</t>
+          <t>suchomimus</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Monolophosaurus jiangi</t>
+          <t>Suchomimus tenerensis</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3034,33 +2998,33 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Rara</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" s="7">
         <f>IF(F51="","",F51-E51)</f>
         <v/>
       </c>
       <c r="H51" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>Cresta de mando</t>
+          <t>Rastreo de orilla</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en juego, tus terópodos ganan +1 de Vida.</t>
+          <t>Cuando entra en juego descarta 1 carta del mazo de tu rival.</t>
         </is>
       </c>
       <c r="L51" s="10" t="inlineStr"/>
@@ -3068,29 +3032,29 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>invictarx</t>
+          <t>eosinopteryx</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Invictarx zephyri</t>
+          <t>Eosinopteryx brevipenna</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Tireóforo</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Rara</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",F52-E52)</f>
@@ -3104,12 +3068,12 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>Formación cerrada</t>
+          <t>Percha compartida</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en juego, tus tireóforos ganan +1 de Vida.</t>
+          <t>Gana +1 de Vida por cada Eosinopteryx que tengas en juego, este incluido.</t>
         </is>
       </c>
       <c r="L52" s="10" t="inlineStr"/>
@@ -3117,48 +3081,48 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>medusaceratops</t>
+          <t>troodon</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Medusaceratops lokii</t>
+          <t>Troodon formosus</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Marginocéfalo</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" s="7">
         <f>IF(F53="","",F53-E53)</f>
         <v/>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>Muralla de golas</t>
+          <t>Caza coordinada</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en juego, tus marginocéfalos ganan +1 de Ataque y +1 de Vida.</t>
+          <t>Gana +1 de Ataque por cada Troodon que tengas en juego, este incluido.</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr"/>
@@ -3166,48 +3130,48 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>platyceratops</t>
+          <t>carnotaurus</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Platyceratops tatarinovi</t>
+          <t>Carnotaurus sastrei</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Marginocéfalo</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",F54-E54)</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>Llamada de manada</t>
+          <t>Territorio exclusivo</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>Al jugarlo, puedes llevarte a la mano otro Platyceratops de tu mazo.</t>
+          <t>Para jugarlo tienes que descartar 2 cartas de tu mano.</t>
         </is>
       </c>
       <c r="L54" s="10" t="inlineStr"/>
@@ -3215,48 +3179,48 @@
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>loricatosaurus</t>
+          <t>spinosaurus</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Loricatosaurus priscus</t>
+          <t>Spinosaurus aegyptiacus</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Tireóforo</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" s="7">
         <f>IF(F55="","",F55-E55)</f>
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>8</v>
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>Terraplén</t>
+          <t>Draga el río</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego tu hábitat recupera 2 puntos.</t>
+          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
         </is>
       </c>
       <c r="L55" s="10" t="inlineStr"/>
@@ -3264,48 +3228,48 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>therizinosaurus</t>
+          <t>mosasaurus</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Therizinosaurus cheloniformis</t>
+          <t>Mosasaurus hoffmannii</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Reptil marino</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" s="7">
         <f>IF(F56="","",F56-E56)</f>
         <v/>
       </c>
       <c r="H56" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>Garra de sequía</t>
+          <t>Draga el río</t>
         </is>
       </c>
       <c r="K56" s="10" t="inlineStr">
         <is>
-          <t>Gana +3 de Ataque mientras haya un clima en el campo.</t>
+          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
         </is>
       </c>
       <c r="L56" s="10" t="inlineStr"/>
@@ -3313,17 +3277,17 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>alaskacephale</t>
+          <t>halszkaraptor</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Alaskacephale gangloffi</t>
+          <t>Halszkaraptor escuilliei</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Marginocéfalo</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -3332,10 +3296,10 @@
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" s="7">
         <f>IF(F57="","",F57-E57)</f>
@@ -3345,16 +3309,16 @@
         <v>2</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>Testarazo</t>
+          <t>Nadador de temporal</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego hiere en 2 al dinosaurio de enfrente.</t>
+          <t>Gana +2 de Vida mientras haya un clima en el campo.</t>
         </is>
       </c>
       <c r="L57" s="10" t="inlineStr"/>
@@ -3362,48 +3326,48 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>titanoceratops</t>
+          <t>tongtianlong</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Titanoceratops ouranos</t>
+          <t>Tongtianlong limosus</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Marginocéfalo</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G58" s="7">
         <f>IF(F58="","",F58-E58)</f>
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>Cuerno mayor</t>
+          <t>Nadador de temporal</t>
         </is>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>Gana +1 de Ataque por cada marginocéfalo que tengas en juego, este incluido.</t>
+          <t>Gana +2 de Ataque mientras haya un clima en el campo.</t>
         </is>
       </c>
       <c r="L58" s="10" t="inlineStr"/>
@@ -3411,48 +3375,48 @@
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>atlasaurus</t>
+          <t>scanisaurus</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Atlasaurus imelakei</t>
+          <t>Scanisaurus nazarowi</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Saurópodo</t>
+          <t>Reptil marino</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" s="7">
         <f>IF(F59="","",F59-E59)</f>
         <v/>
       </c>
       <c r="H59" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>Sombra del cuello</t>
+          <t>Banco de caza</t>
         </is>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en juego, tus saurópodos ganan +1 de Vida.</t>
+          <t>Mientras esté en juego, tus reptiles marinos ganan +1 de Ataque.</t>
         </is>
       </c>
       <c r="L59" s="10" t="inlineStr"/>
@@ -3460,48 +3424,48 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>stegoceras</t>
+          <t>monolophosaurus</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Stegoceras validum</t>
+          <t>Monolophosaurus jiangi</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Marginocéfalo</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60" s="7">
         <f>IF(F60="","",F60-E60)</f>
         <v/>
       </c>
       <c r="H60" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>Cabezazo de vuelta</t>
+          <t>Cresta de mando</t>
         </is>
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>Devuelve 2 de daño a quien lo hiera en combate.</t>
+          <t>Mientras esté en juego, tus terópodos ganan +1 de Vida.</t>
         </is>
       </c>
       <c r="L60" s="10" t="inlineStr"/>
@@ -3509,22 +3473,22 @@
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>maiasaura</t>
+          <t>invictarx</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Maiasaura peeblesorum</t>
+          <t>Invictarx zephyri</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Ornitópodo</t>
+          <t>Tireóforo</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3538,19 +3502,19 @@
         <v/>
       </c>
       <c r="H61" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>Buena madre</t>
+          <t>Formación cerrada</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>Al final de tu turno, todos tus dinosaurios recuperan 1 de Vida.</t>
+          <t>Mientras esté en juego, tus tireóforos ganan +1 de Vida.</t>
         </is>
       </c>
       <c r="L61" s="10" t="inlineStr"/>
@@ -3558,29 +3522,29 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>edmontosaurus</t>
+          <t>medusaceratops</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Edmontosaurus annectens</t>
+          <t>Medusaceratops lokii</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Ornitópodo</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62" s="7">
         <f>IF(F62="","",F62-E62)</f>
@@ -3594,12 +3558,12 @@
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>Migración en masa</t>
+          <t>Muralla de golas</t>
         </is>
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en juego, tus ornitópodos ganan +1 de Ataque y +1 de Vida.</t>
+          <t>Mientras esté en juego, tus marginocéfalos ganan +1 de Ataque y +1 de Vida.</t>
         </is>
       </c>
       <c r="L62" s="10" t="inlineStr"/>
@@ -3607,17 +3571,17 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>plateosauravus</t>
+          <t>platyceratops</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Plateosauravus cullingworthi</t>
+          <t>Platyceratops tatarinovi</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Saurópodo</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -3626,29 +3590,29 @@
         </is>
       </c>
       <c r="E63" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" s="7">
         <f>IF(F63="","",F63-E63)</f>
         <v/>
       </c>
       <c r="H63" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="8" t="n">
         <v>2</v>
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>Colonia de ribera</t>
+          <t>Llamada de manada</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>Gana +1 de Ataque y +1 de Vida por cada Plateosauravus que tengas en juego, este incluido.</t>
+          <t>Al jugarlo, puedes llevarte a la mano otro Platyceratops de tu mazo.</t>
         </is>
       </c>
       <c r="L63" s="10" t="inlineStr"/>
@@ -3656,12 +3620,12 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>gargoyleosaurus</t>
+          <t>loricatosaurus</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Gargoyleosaurus parkpinorum</t>
+          <t>Loricatosaurus priscus</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -3671,33 +3635,33 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Rara</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" s="7">
         <f>IF(F64="","",F64-E64)</f>
         <v/>
       </c>
       <c r="H64" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>Osteodermos</t>
+          <t>Terraplén</t>
         </is>
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>Devuelve 3 de daño a quien lo hiera en combate.</t>
+          <t>Cuando entra en juego tu hábitat recupera 2 puntos.</t>
         </is>
       </c>
       <c r="L64" s="10" t="inlineStr"/>
@@ -3705,22 +3669,22 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>wendiceratops</t>
+          <t>therizinosaurus</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Wendiceratops pinhornensis</t>
+          <t>Therizinosaurus cheloniformis</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Marginocéfalo</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3734,19 +3698,19 @@
         <v/>
       </c>
       <c r="H65" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>Embestida</t>
+          <t>Garra de sequía</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego manda al descarte 1 dinosaurio rival de hasta 2 de Vida.</t>
+          <t>Gana +3 de Ataque mientras haya un clima en el campo.</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr"/>
@@ -3754,29 +3718,29 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>antarctosaurus</t>
+          <t>alaskacephale</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Antarctosaurus wichmannianus</t>
+          <t>Alaskacephale gangloffi</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Saurópodo</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G66" s="7">
         <f>IF(F66="","",F66-E66)</f>
@@ -3786,16 +3750,16 @@
         <v>2</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>Refugio polar</t>
+          <t>Testarazo</t>
         </is>
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en juego, a ninguno de tus dinosaurios le afectan los efectos del clima.</t>
+          <t>Cuando entra en juego hiere en 2 al dinosaurio de enfrente.</t>
         </is>
       </c>
       <c r="L66" s="10" t="inlineStr"/>
@@ -3803,12 +3767,12 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>liaoceratops</t>
+          <t>titanoceratops</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Liaoceratops yanzigouensis</t>
+          <t>Titanoceratops ouranos</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3818,33 +3782,33 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" s="7">
         <f>IF(F67="","",F67-E67)</f>
         <v/>
       </c>
       <c r="H67" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>Grito de aviso</t>
+          <t>Cuerno mayor</t>
         </is>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>Al jugarlo, puedes llevarte a la mano un marginocéfalo de tu mazo.</t>
+          <t>Gana +1 de Ataque por cada marginocéfalo que tengas en juego, este incluido.</t>
         </is>
       </c>
       <c r="L67" s="10" t="inlineStr"/>
@@ -3852,17 +3816,17 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>rhinorex</t>
+          <t>atlasaurus</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Rhinorex condrupus</t>
+          <t>Atlasaurus imelakei</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Ornitópodo</t>
+          <t>Saurópodo</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -3881,19 +3845,19 @@
         <v/>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>Última llanura</t>
+          <t>Sombra del cuello</t>
         </is>
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
-          <t>Gana +2 de Ataque mientras tu hábitat esté por debajo del de tu rival.</t>
+          <t>Mientras esté en juego, tus saurópodos ganan +1 de Vida.</t>
         </is>
       </c>
       <c r="L68" s="10" t="inlineStr"/>
@@ -3901,17 +3865,17 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>bienosaurus</t>
+          <t>stegoceras</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Bienosaurus lufengensis</t>
+          <t>Stegoceras validum</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Tireóforo</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -3920,10 +3884,10 @@
         </is>
       </c>
       <c r="E69" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="7">
         <f>IF(F69="","",F69-E69)</f>
@@ -3933,16 +3897,16 @@
         <v>1</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>Cría acorazada</t>
+          <t>Cabezazo de vuelta</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Gana +1 de Vida por cada tireóforo que tengas en juego, este incluido.</t>
+          <t>Devuelve 2 de daño a quien lo hiera en combate.</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr"/>
@@ -3950,12 +3914,12 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>shuangmiaosaurus</t>
+          <t>maiasaura</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Shuangmiaosaurus gilmorei</t>
+          <t>Maiasaura peeblesorum</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -3965,33 +3929,33 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70" s="7">
         <f>IF(F70="","",F70-E70)</f>
         <v/>
       </c>
       <c r="H70" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>Ramoneo de orilla</t>
+          <t>Buena madre</t>
         </is>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego tu hábitat recupera 1 punto.</t>
+          <t>Al final de tu turno, todos tus dinosaurios recuperan 1 de Vida.</t>
         </is>
       </c>
       <c r="L70" s="10" t="inlineStr"/>
@@ -3999,29 +3963,29 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>chasmosaurus</t>
+          <t>edmontosaurus</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Chasmosaurus belli</t>
+          <t>Edmontosaurus annectens</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Marginocéfalo</t>
+          <t>Ornitópodo</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G71" s="7">
         <f>IF(F71="","",F71-E71)</f>
@@ -4031,16 +3995,16 @@
         <v>2</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>Vigía de la gola</t>
+          <t>Migración en masa</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>Cuando entra en juego robas 1 carta.</t>
+          <t>Mientras esté en juego, tus ornitópodos ganan +1 de Ataque y +1 de Vida.</t>
         </is>
       </c>
       <c r="L71" s="10" t="inlineStr"/>
@@ -4048,17 +4012,17 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>biomasa</t>
+          <t>plateosauravus</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Pradera de helechos</t>
+          <t>Plateosauravus cullingworthi</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Saurópodo</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -4067,25 +4031,29 @@
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="7">
         <f>IF(F72="","",F72-E72)</f>
         <v/>
       </c>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n"/>
+      <c r="H72" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>Pradera de helechos</t>
+          <t>Colonia de ribera</t>
         </is>
       </c>
       <c r="K72" s="10" t="inlineStr">
         <is>
-          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+          <t>Gana +1 de Ataque y +1 de Vida por cada Plateosauravus que tengas en juego, este incluido.</t>
         </is>
       </c>
       <c r="L72" s="10" t="inlineStr"/>
@@ -4093,44 +4061,48 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>araucarias</t>
+          <t>gargoyleosaurus</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Bosque de araucarias</t>
+          <t>Gargoyleosaurus parkpinorum</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Tireóforo</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="7">
         <f>IF(F73="","",F73-E73)</f>
         <v/>
       </c>
-      <c r="H73" s="7" t="n"/>
-      <c r="I73" s="7" t="n"/>
+      <c r="H73" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>Bosque de araucarias</t>
+          <t>Osteodermos</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+          <t>Devuelve 3 de daño a quien lo hiera en combate.</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr"/>
@@ -4138,44 +4110,48 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>ginkgos</t>
+          <t>wendiceratops</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Arboleda de ginkgos</t>
+          <t>Wendiceratops pinhornensis</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G74" s="7">
         <f>IF(F74="","",F74-E74)</f>
         <v/>
       </c>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
+      <c r="H74" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>Arboleda de ginkgos</t>
+          <t>Embestida</t>
         </is>
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
-          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+          <t>Cuando entra en juego manda al descarte 1 dinosaurio rival de hasta 2 de Vida.</t>
         </is>
       </c>
       <c r="L74" s="10" t="inlineStr"/>
@@ -4183,44 +4159,48 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>cicadas</t>
+          <t>antarctosaurus</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Matorral de cícadas</t>
+          <t>Antarctosaurus wichmannianus</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Saurópodo</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G75" s="7">
         <f>IF(F75="","",F75-E75)</f>
         <v/>
       </c>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="7" t="n"/>
+      <c r="H75" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>12</v>
+      </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>Matorral de cícadas</t>
+          <t>Refugio polar</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+          <t>Mientras esté en juego, a ninguno de tus dinosaurios le afectan los efectos del clima.</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr"/>
@@ -4228,17 +4208,17 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>equisetos</t>
+          <t>liaoceratops</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Juncal de equisetos</t>
+          <t>Liaoceratops yanzigouensis</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -4247,25 +4227,29 @@
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="7">
         <f>IF(F76="","",F76-E76)</f>
         <v/>
       </c>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
+      <c r="H76" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>Juncal de equisetos</t>
+          <t>Grito de aviso</t>
         </is>
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
-          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+          <t>Al jugarlo, puedes llevarte a la mano un marginocéfalo de tu mazo.</t>
         </is>
       </c>
       <c r="L76" s="10" t="inlineStr"/>
@@ -4273,44 +4257,48 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>galeria</t>
+          <t>rhinorex</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Bosque de galería</t>
+          <t>Rhinorex condrupus</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Ornitópodo</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G77" s="7">
         <f>IF(F77="","",F77-E77)</f>
         <v/>
       </c>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="n"/>
+      <c r="H77" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>Bosque de galería</t>
+          <t>Última llanura</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+          <t>Gana +2 de Ataque mientras tu hábitat esté por debajo del de tu rival.</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr"/>
@@ -4318,17 +4306,17 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>helechal</t>
+          <t>bienosaurus</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Helechal arborescente</t>
+          <t>Bienosaurus lufengensis</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Tireóforo</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -4337,25 +4325,29 @@
         </is>
       </c>
       <c r="E78" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="7">
         <f>IF(F78="","",F78-E78)</f>
         <v/>
       </c>
-      <c r="H78" s="7" t="n"/>
-      <c r="I78" s="7" t="n"/>
+      <c r="H78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>Helechal arborescente</t>
+          <t>Cría acorazada</t>
         </is>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
-          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+          <t>Gana +1 de Vida por cada tireóforo que tengas en juego, este incluido.</t>
         </is>
       </c>
       <c r="L78" s="10" t="inlineStr"/>
@@ -4363,44 +4355,48 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>vega</t>
+          <t>shuangmiaosaurus</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Vega de aluvión</t>
+          <t>Shuangmiaosaurus gilmorei</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Ornitópodo</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="7">
         <f>IF(F79="","",F79-E79)</f>
         <v/>
       </c>
-      <c r="H79" s="7" t="n"/>
-      <c r="I79" s="7" t="n"/>
+      <c r="H79" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>Vega de aluvión</t>
+          <t>Ramoneo de orilla</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>+2 Biomasa al bajarla. Pierdes 2 cartas de tu mazo. Una por turno.</t>
+          <t>Cuando entra en juego tu hábitat recupera 1 punto.</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr"/>
@@ -4408,44 +4404,48 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>humedal</t>
+          <t>chasmosaurus</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Humedal de tierras bajas</t>
+          <t>Chasmosaurus belli</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="7">
         <f>IF(F80="","",F80-E80)</f>
         <v/>
       </c>
-      <c r="H80" s="7" t="n"/>
-      <c r="I80" s="7" t="n"/>
+      <c r="H80" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>Humedal de tierras bajas</t>
+          <t>Vigía de la gola</t>
         </is>
       </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
-          <t>+2 Biomasa al bajarla. Pierdes 2 cartas de tu mazo. Una por turno.</t>
+          <t>Cuando entra en juego robas 1 carta.</t>
         </is>
       </c>
       <c r="L80" s="10" t="inlineStr"/>
@@ -4453,17 +4453,17 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>manantial</t>
+          <t>tyrannosaurus</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Manantial perenne</t>
+          <t>Tyrannosaurus rex</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Biomasa</t>
+          <t>Terópodo</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -4472,45 +4472,1234 @@
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G81" s="7">
         <f>IF(F81="","",F81-E81)</f>
         <v/>
       </c>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="n"/>
+      <c r="H81" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I81" s="8" t="n">
+        <v>9</v>
+      </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
+          <t>Rugido</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego tu rival descarta 2 cartas de su mano al azar.</t>
+        </is>
+      </c>
+      <c r="L81" s="10" t="inlineStr"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>velociraptor</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Velociraptor mongoliensis</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="7">
+        <f>IF(F82="","",F82-E82)</f>
+        <v/>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>Garra impaciente</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>Para jugarlo tienes que descartar 1 carta de tu mano.</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="inlineStr"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>brachiosaurus</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Brachiosaurus altithorax</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Legendaria</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" s="7">
+        <f>IF(F83="","",F83-E83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>Sombra del gigante</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, todos tus dinosaurios ganan +1 de Vida.</t>
+        </is>
+      </c>
+      <c r="L83" s="10" t="inlineStr"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>argentinosaurus</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Argentinosaurus huinculensis</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" s="7">
+        <f>IF(F84="","",F84-E84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I84" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>Peso muerto</t>
+        </is>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>Para jugarlo tienes que descartar 2 cartas de tu mano.</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>mamenchisaurus</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Mamenchisaurus hochuanensis</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Rara</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" s="7">
+        <f>IF(F85="","",F85-E85)</f>
+        <v/>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>Cuello sin fin</t>
+        </is>
+      </c>
+      <c r="K85" s="10" t="inlineStr">
+        <is>
+          <t>Al final de tu turno recupera 1 de Vida.</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="inlineStr"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>amargasaurus</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Amargasaurus cazadorensis</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Rara</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="7">
+        <f>IF(F86="","",F86-E86)</f>
+        <v/>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>Rebaño de cuellos</t>
+        </is>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Vida por cada saurópodo que tengas en juego, este incluido.</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="inlineStr"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>ankylosaurus</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Ankylosaurus magniventris</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Tireóforo</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Legendaria</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G87" s="7">
+        <f>IF(F87="","",F87-E87)</f>
+        <v/>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>Maza de cola</t>
+        </is>
+      </c>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
+          <t>Devuelve 4 de daño a quien lo hiera en combate.</t>
+        </is>
+      </c>
+      <c r="L87" s="10" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>kentrosaurus</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Kentrosaurus aethiopicus</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Tireóforo</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="7">
+        <f>IF(F88="","",F88-E88)</f>
+        <v/>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>Púas de hombro</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>Devuelve 1 de daño a quien lo hiera en combate.</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="inlineStr"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>euoplocephalus</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Euoplocephalus tutus</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Tireóforo</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Rara</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" s="7">
+        <f>IF(F89="","",F89-E89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>Párpados de hueso</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>No le afectan las cartas de evento de tu rival.</t>
+        </is>
+      </c>
+      <c r="L89" s="10" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>triceratops</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Triceratops horridus</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" s="7">
+        <f>IF(F90="","",F90-E90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I90" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>Tres cuernos</t>
+        </is>
+      </c>
+      <c r="K90" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego manda al descarte 1 dinosaurio rival de hasta 3 de Vida.</t>
+        </is>
+      </c>
+      <c r="L90" s="10" t="inlineStr"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>pachycephalosaurus</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Pachycephalosaurus wyomingensis</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Rara</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" s="7">
+        <f>IF(F91="","",F91-E91)</f>
+        <v/>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I91" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>Cabezazo</t>
+        </is>
+      </c>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego hiere en 3 al dinosaurio de enfrente.</t>
+        </is>
+      </c>
+      <c r="L91" s="10" t="inlineStr"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>iguanodon</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Iguanodon bernissartensis</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Ornitópodo</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Rara</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" s="7">
+        <f>IF(F92="","",F92-E92)</f>
+        <v/>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>Manada de Bernissart</t>
+        </is>
+      </c>
+      <c r="K92" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque por cada Iguanodon en juego, sea de quien sea y este incluido.</t>
+        </is>
+      </c>
+      <c r="L92" s="10" t="inlineStr"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>parasaurolophus</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Parasaurolophus walkeri</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Ornitópodo</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Rara</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" s="7">
+        <f>IF(F93="","",F93-E93)</f>
+        <v/>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I93" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>Llamada resonante</t>
+        </is>
+      </c>
+      <c r="K93" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego robas 1 carta y tu hábitat recupera 1 punto.</t>
+        </is>
+      </c>
+      <c r="L93" s="10" t="inlineStr"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>pteranodon</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Pteranodon longiceps</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Pterosaurio</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="7">
+        <f>IF(F94="","",F94-E94)</f>
+        <v/>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>Planeo</t>
+        </is>
+      </c>
+      <c r="K94" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego pierdes 1 carta de tu mazo y robas 1.</t>
+        </is>
+      </c>
+      <c r="L94" s="10" t="inlineStr"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>quetzalcoatlus</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Quetzalcoatlus northropi</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Pterosaurio</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="7">
+        <f>IF(F95="","",F95-E95)</f>
+        <v/>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>Sombra en la llanura</t>
+        </is>
+      </c>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego tu rival pierde 3 cartas del mazo.</t>
+        </is>
+      </c>
+      <c r="L95" s="10" t="inlineStr"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>elasmosaurus</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Elasmosaurus platyurus</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Reptil marino</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Rara</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" s="7">
+        <f>IF(F96="","",F96-E96)</f>
+        <v/>
+      </c>
+      <c r="H96" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>Cuello de vigía</t>
+        </is>
+      </c>
+      <c r="K96" s="10" t="inlineStr">
+        <is>
+          <t>Resta 1 a cada golpe que llegue a tu hábitat.</t>
+        </is>
+      </c>
+      <c r="L96" s="10" t="inlineStr"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>biomasa</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Pradera de helechos</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="7">
+        <f>IF(F97="","",F97-E97)</f>
+        <v/>
+      </c>
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>Pradera de helechos</t>
+        </is>
+      </c>
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L97" s="10" t="inlineStr"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>araucarias</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Bosque de araucarias</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="7">
+        <f>IF(F98="","",F98-E98)</f>
+        <v/>
+      </c>
+      <c r="H98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>Bosque de araucarias</t>
+        </is>
+      </c>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L98" s="10" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>ginkgos</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Arboleda de ginkgos</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="7">
+        <f>IF(F99="","",F99-E99)</f>
+        <v/>
+      </c>
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>Arboleda de ginkgos</t>
+        </is>
+      </c>
+      <c r="K99" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L99" s="10" t="inlineStr"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>cicadas</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Matorral de cícadas</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="7">
+        <f>IF(F100="","",F100-E100)</f>
+        <v/>
+      </c>
+      <c r="H100" s="7" t="n"/>
+      <c r="I100" s="7" t="n"/>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>Matorral de cícadas</t>
+        </is>
+      </c>
+      <c r="K100" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L100" s="10" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>equisetos</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Juncal de equisetos</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="7">
+        <f>IF(F101="","",F101-E101)</f>
+        <v/>
+      </c>
+      <c r="H101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>Juncal de equisetos</t>
+        </is>
+      </c>
+      <c r="K101" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L101" s="10" t="inlineStr"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>galeria</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Bosque de galería</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="7">
+        <f>IF(F102="","",F102-E102)</f>
+        <v/>
+      </c>
+      <c r="H102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>Bosque de galería</t>
+        </is>
+      </c>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L102" s="10" t="inlineStr"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>helechal</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Helechal arborescente</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="7">
+        <f>IF(F103="","",F103-E103)</f>
+        <v/>
+      </c>
+      <c r="H103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>Helechal arborescente</t>
+        </is>
+      </c>
+      <c r="K103" s="10" t="inlineStr">
+        <is>
+          <t>+1 Biomasa al bajarla. Pierdes 1 carta de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L103" s="10" t="inlineStr"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>vega</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Vega de aluvión</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="7">
+        <f>IF(F104="","",F104-E104)</f>
+        <v/>
+      </c>
+      <c r="H104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>Vega de aluvión</t>
+        </is>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
+          <t>+2 Biomasa al bajarla. Pierdes 2 cartas de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L104" s="10" t="inlineStr"/>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>humedal</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Humedal de tierras bajas</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="7">
+        <f>IF(F105="","",F105-E105)</f>
+        <v/>
+      </c>
+      <c r="H105" s="7" t="n"/>
+      <c r="I105" s="7" t="n"/>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>Humedal de tierras bajas</t>
+        </is>
+      </c>
+      <c r="K105" s="10" t="inlineStr">
+        <is>
+          <t>+2 Biomasa al bajarla. Pierdes 2 cartas de tu mazo. Una por turno.</t>
+        </is>
+      </c>
+      <c r="L105" s="10" t="inlineStr"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>manantial</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
           <t>Manantial perenne</t>
         </is>
       </c>
-      <c r="K81" s="10" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Biomasa</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Legendaria</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="7">
+        <f>IF(F106="","",F106-E106)</f>
+        <v/>
+      </c>
+      <c r="H106" s="7" t="n"/>
+      <c r="I106" s="7" t="n"/>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>Manantial perenne</t>
+        </is>
+      </c>
+      <c r="K106" s="10" t="inlineStr">
         <is>
           <t>+3 Biomasa al bajarla. Pierdes 3 cartas de tu mazo. Una por turno.</t>
         </is>
       </c>
-      <c r="L81" s="10" t="inlineStr"/>
+      <c r="L106" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K81"/>
+  <autoFilter ref="A5:K106"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="F6:F81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
+    <dataValidation sqref="F6:F106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>8</formula2>
     </dataValidation>
-    <dataValidation sqref="H6:I81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque y Vida van de 0 a 20." type="whole" operator="between">
+    <dataValidation sqref="H6:I106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque y Vida van de 0 a 20." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation sqref="D6:D81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
+    <dataValidation sqref="D6:D106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
       <formula1>"Común,Rara,Épica,Legendaria"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4525,7 +5714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4618,7 +5807,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bruma de valle</t>
+          <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -4626,32 +5815,32 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Bruma de valle</t>
+          <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>+1 de Vida a todos los dinosaurios del campo, mientras siga en el campo.</t>
+          <t>Tu rival descarta 2 cartas de su mano al azar.</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Vida a todos los del campo</t>
+          <t>cartas que el rival descarta de la mano</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.canalVida</t>
+          <t>rasgos.bosqueRiberenoMano</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -4659,26 +5848,32 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+          <t>+1 de Vida a todos los dinosaurios del campo, mientras siga en el campo.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+          <t>Vida a todos los del campo</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>efectosCampo.canalVida</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Canal fluvial trenzado</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -4686,12 +5881,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Canal fluvial trenzado</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
+          <t>Todos tus dinosaurios recuperan 2 de Vida.</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -4699,19 +5894,19 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Vida que se quita, a dos rivales</t>
+          <t>Vida que recuperan todos los tuyos</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>rasgos.competenciaVida</t>
+          <t>rasgos.canalTrenzadoCura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Crecida estacional</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -4719,32 +5914,26 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Crecida estacional</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>cambio de carta por turno y jugador</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>efectosCampo.llanuraReciclaPorTurno</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Crecimiento acelerado</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -4752,12 +5941,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Crecimiento acelerado</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
+          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -4765,19 +5954,19 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Ataque, y otro tanto de Vida</t>
+          <t>Vida que se quita, a dos rivales</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>rasgos.crecimientoAtaque</t>
+          <t>rasgos.competenciaVida</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Estación de lluvias</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -4785,12 +5974,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Estación de lluvias</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
+          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -4798,19 +5987,19 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>heridas que curan los saurópodos</t>
+          <t>cambio de carta por turno y jugador</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.bosqueCura</t>
+          <t>efectosCampo.llanuraReciclaPorTurno</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Fractura consolidada</t>
+          <t>Crecimiento acelerado</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -4818,12 +6007,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Fractura consolidada</t>
+          <t>Crecimiento acelerado</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>−2 Poder permanente a un dinosaurio rival.</t>
+          <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -4831,19 +6020,19 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Ataque que se quita</t>
+          <t>Ataque, y otro tanto de Vida</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>rasgos.fracturaAtaque</t>
+          <t>rasgos.crecimientoAtaque</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Gastrolitos</t>
+          <t>Deriva árida</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -4851,32 +6040,26 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Gastrolitos</t>
+          <t>Deriva árida</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Cura +1 de vida a un dinosaurio al final del turno</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>Ambos jugadores descartan la mano entera y roban otras tantas cartas.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>heridas curadas a un dinosaurio</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.gastrolitosCura</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Gregarismo</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -4884,12 +6067,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Gregarismo</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
+          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -4897,19 +6080,19 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Ataque a toda la especie</t>
+          <t>heridas que curan los saurópodos</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>rasgos.gregarismoAtaque</t>
+          <t>efectosCampo.bosqueCura</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Lago efímero</t>
+          <t>Fractura consolidada</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -4917,26 +6100,32 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Lago efímero</t>
+          <t>Fractura consolidada</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
+          <t>−2 Poder permanente a un dinosaurio rival.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
+          <t>Ataque que se quita</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.fracturaAtaque</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Monzón de verano</t>
+          <t>Frutos de cícada</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -4944,32 +6133,32 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Monzón de verano</t>
+          <t>Frutos de cícada</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
+          <t>+3 Biomasa ahora mismo. Tu rival roba 1 carta.</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Biomasa por turno a los DOS</t>
+          <t>Biomasa, y el rival roba 1</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.sabanaBiomasa</t>
+          <t>recursos.frutosBiomasa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mortandad estacional</t>
+          <t>Gastrolitos</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -4977,32 +6166,32 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mortandad estacional</t>
+          <t>Gastrolitos</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
+          <t>Cura +1 de vida a un dinosaurio al final del turno</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>de daño a TODOS, incluidos los tuyos</t>
+          <t>heridas curadas a un dinosaurio</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>rasgos.mortandadDano</t>
+          <t>rasgos.gastrolitosCura</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Neumaticidad ósea</t>
+          <t>Gregarismo</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -5010,32 +6199,32 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Neumaticidad ósea</t>
+          <t>Gregarismo</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
+          <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Ataque permanente</t>
+          <t>Ataque a toda la especie</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>rasgos.neumaticidadAtaque</t>
+          <t>rasgos.gregarismoAtaque</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Rebrote tras incendio</t>
+          <t>Lago efímero</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -5043,12 +6232,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Rebrote tras incendio</t>
+          <t>Lago efímero</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
+          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -5062,7 +6251,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Sequía prolongada</t>
+          <t>Llanura de inundación</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
@@ -5070,16 +6259,16 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Sequía prolongada</t>
+          <t>Llanura de inundación</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Durante 3 turnos, ambos jugadores pierden 1 carta del mazo al robar.</t>
+          <t>Ambos jugadores pierden 3 cartas del mazo. Tú robas 1.</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -5088,38 +6277,329 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.aridezMazo</t>
+          <t>rasgos.inundacionMazo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>Manada de paso</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Manada de paso</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>+2 Biomasa ahora mismo. Pierdes 3 cartas de tu mazo.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Biomasa, a cambio de 3 cartas del mazo</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>recursos.manadaPasoBiomasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Monzón de verano</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Monzón de verano</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Biomasa por turno a los DOS</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>efectosCampo.sabanaBiomasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Mortandad estacional</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Mortandad estacional</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>de daño a TODOS, incluidos los tuyos</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.mortandadDano</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Neumaticidad ósea</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Neumaticidad ósea</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Ataque permanente</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.neumaticidadAtaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Nido con huevos</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Nido con huevos</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Robas 2 cartas.</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>cartas que robas</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.nidoRoba</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nube de insectos</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Nube de insectos</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>+1 Biomasa ahora mismo. Robas 1 carta.</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Biomasa, y además robas 1</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>recursos.insectosBiomasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Rebrote tras incendio</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Rebrote tras incendio</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sabana de helechos</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Sabana de helechos</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Robas 2 cartas. Luego descartas 1 carta de tu mano al azar.</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>cartas que robas (y descartas 1)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.sabanaHelechosRoba</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Sequía prolongada</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Sequía prolongada</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Durante 3 turnos, ambos jugadores pierden 1 carta del mazo al robar.</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>cartas de mazo que pierden los DOS</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>efectosCampo.aridezMazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="B30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E30" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>cartas que pierde el rival</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>rasgos.trampaMazoRival</t>
         </is>
@@ -5139,7 +6619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5227,11 +6707,11 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Antarctosaurus wichmannianus</t>
+          <t>Antarctosaurus wichmannianus, Brachiosaurus altithorax</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5277,11 +6757,11 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Carnotaurus sastrei</t>
+          <t>Carnotaurus sastrei, Velociraptor mongoliensis, Argentinosaurus huinculensis</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5302,11 +6782,11 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Dryosaurus altus, Stegosaurus stenops, Dromaeosaurus albertensis, Eosinopteryx brevipenna, Troodon formosus, Plateosauravus cullingworthi</t>
+          <t>Dryosaurus altus, Stegosaurus stenops, Dromaeosaurus albertensis, Eosinopteryx brevipenna, Troodon formosus, Plateosauravus cullingworthi, Iguanodon bernissartensis</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -5327,11 +6807,11 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Titanoceratops ouranos, Bienosaurus lufengensis</t>
+          <t>Titanoceratops ouranos, Bienosaurus lufengensis, Amargasaurus cazadorensis</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5377,11 +6857,11 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Ornitholestes hermanni, Ojoraptorsaurus boerei, Alaskacephale gangloffi</t>
+          <t>Ornitholestes hermanni, Ojoraptorsaurus boerei, Alaskacephale gangloffi, Pachycephalosaurus wyomingensis</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -5402,11 +6882,11 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Tyrannotitan chubutensis, Wendiceratops pinhornensis</t>
+          <t>Tyrannotitan chubutensis, Wendiceratops pinhornensis, Triceratops horridus</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -5423,7 +6903,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Al entrar · mueleRival + muelePropio</t>
+          <t>Al entrar · manoRival</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -5431,12 +6911,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Spinosaurus aegyptiacus, Mosasaurus hoffmannii</t>
+          <t>Allosaurus fragilis, Tyrannosaurus rex</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
+          <t>Cuando entra en juego descarta 1 carta al azar de la mano de tu rival.</t>
         </is>
       </c>
     </row>
@@ -5448,7 +6928,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Al entrar · roba</t>
+          <t>Al entrar · mueleRival</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -5456,12 +6936,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Huaxiadraco corollatus, Chasmosaurus belli</t>
+          <t>Suchomimus tenerensis, Quetzalcoatlus northropi</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Cuando entra en juego robas 1 carta.</t>
+          <t>Cuando entra en juego descarta 1 carta del mazo de tu rival.</t>
         </is>
       </c>
     </row>
@@ -5473,20 +6953,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Al entrar · manoRival</t>
+          <t>Al entrar · mueleRival + muelePropio</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Allosaurus fragilis</t>
+          <t>Spinosaurus aegyptiacus, Mosasaurus hoffmannii</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Cuando entra en juego descarta 1 carta al azar de la mano de tu rival.</t>
+          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
         </is>
       </c>
     </row>
@@ -5498,20 +6978,20 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Al entrar · muelePropio</t>
+          <t>Al entrar · roba</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Ceratosaurus nasicornis</t>
+          <t>Huaxiadraco corollatus, Chasmosaurus belli</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Cuando entra en juego descarta 2 cartas de tu mazo.</t>
+          <t>Cuando entra en juego robas 1 carta.</t>
         </is>
       </c>
     </row>
@@ -5523,7 +7003,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Al entrar · mueleRival</t>
+          <t>Al entrar · muelePropio</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -5531,99 +7011,99 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Suchomimus tenerensis</t>
+          <t>Ceratosaurus nasicornis</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Cuando entra en juego descarta 1 carta del mazo de tu rival.</t>
+          <t>Cuando entra en juego descarta 2 cartas de tu mazo.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>espinas</t>
+          <t>entrada</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Devuelve daño</t>
+          <t>Al entrar · muelePropio + roba</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Stegoceras validum, Gargoyleosaurus parkpinorum</t>
+          <t>Pteranodon longiceps</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Devuelve 2 de daño a quien lo hiera en combate.</t>
+          <t>Cuando entra en juego pierdes 1 carta de tu mazo y robas 1.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>inmune</t>
+          <t>entrada</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Inmunidad a CLIMA</t>
+          <t>Al entrar · roba + curaHabitat</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Torvosaurus tanneri, Nodosaurus textilis</t>
+          <t>Parasaurolophus walkeri</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>No le afectan los efectos del clima.</t>
+          <t>Cuando entra en juego robas 1 carta y tu hábitat recupera 1 punto.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>inmune</t>
+          <t>espinas</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Inmunidad a EVENTO</t>
+          <t>Devuelve daño</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Riparovenator milnerae, Lokiceratops rangiformis</t>
+          <t>Stegoceras validum, Gargoyleosaurus parkpinorum, Ankylosaurus magniventris, Kentrosaurus aethiopicus</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>No le afectan las cartas de evento de tu rival.</t>
+          <t>Devuelve 2 de daño a quien lo hiera en combate.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>regenera</t>
+          <t>guardia</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Cura a los tuyos</t>
+          <t>Guardia del hábitat</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -5631,99 +7111,99 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Maiasaura peeblesorum</t>
+          <t>Elasmosaurus platyurus</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Al final de tu turno, todos tus dinosaurios recuperan 1 de Vida.</t>
+          <t>Resta 1 a cada golpe que llegue a tu hábitat.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>regenera</t>
+          <t>inmune</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Se cura sola</t>
+          <t>Inmunidad a EVENTO</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Camarasaurus grandis</t>
+          <t>Riparovenator milnerae, Lokiceratops rangiformis, Euoplocephalus tutus</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Al final de tu turno recupera 1 de Vida.</t>
+          <t>No le afectan las cartas de evento de tu rival.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>inmune</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Condicional · CLIMA</t>
+          <t>Inmunidad a CLIMA</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Halszkaraptor escuilliei, Tongtianlong limosus, Therizinosaurus cheloniformis</t>
+          <t>Torvosaurus tanneri, Nodosaurus textilis</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Gana +2 de Vida mientras haya un clima en el campo.</t>
+          <t>No le afectan los efectos del clima.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>regenera</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Condicional · ALIADO_CON_VIDA</t>
+          <t>Se cura sola</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Plesiopleurodon wellesi</t>
+          <t>Camarasaurus grandis, Mamenchisaurus hochuanensis</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Gana +2 de Ataque si tienes en juego algún dinosaurio con más de 6 de Vida.</t>
+          <t>Al final de tu turno recupera 1 de Vida.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>regenera</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Condicional · HABITAT_DETRAS</t>
+          <t>Cura a los tuyos</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -5731,35 +7211,110 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Rhinorex condrupus</t>
+          <t>Maiasaura peeblesorum</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Gana +2 de Ataque mientras tu hábitat esté por debajo del de tu rival.</t>
+          <t>Al final de tu turno, todos tus dinosaurios recuperan 1 de Vida.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Condicional · CLIMA</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Halszkaraptor escuilliei, Tongtianlong limosus, Therizinosaurus cheloniformis</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Gana +2 de Vida mientras haya un clima en el campo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Condicional · ALIADO_CON_VIDA</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Plesiopleurodon wellesi</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Gana +2 de Ataque si tienes en juego algún dinosaurio con más de 6 de Vida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Condicional · HABITAT_DETRAS</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Rhinorex condrupus</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Gana +2 de Ataque mientras tu hábitat esté por debajo del de tu rival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>trio</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Umbral permanente</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="C30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Brachylophosaurus canadensis</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Si llegas a tener 3 Brachylophosaurus en juego, éste gana +6 de Ataque para siempre.</t>
         </is>
@@ -6258,13 +7813,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -6279,13 +7834,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -6300,13 +7855,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -6321,13 +7876,13 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -6342,10 +7897,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>5.9</v>
@@ -6363,13 +7918,13 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -6384,13 +7939,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>12.64 turnos</t>
+          <t>11.66 turnos</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>FALLA</t>
+          <t>cumple</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>68.8 %</t>
+          <t>72.1 %</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>FALLA</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>36% / 63% / 0%</t>
+          <t>44% / 56% / 0%</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -698,68 +698,6 @@
           <t>FALLA</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Cartas fuera de banda</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>índice 1,00 es la diana; fuera de 0,70–1,30 está mal</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Bruma de valle</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>índice 0.00, uso 0 % (coste 1)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Competencia trófica</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>índice 0.00, uso 0 % (coste 3)</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sequía prolongada</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>índice 0.51, uso 45 % (coste 1)</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7967,7 +7905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8017,7 +7955,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -8033,27 +7971,27 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>nodosaurus</t>
+          <t>stegosaurus</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>stegosaurus</t>
+          <t>kentrosaurus</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>allosaurus</t>
+          <t>velociraptor</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -8063,7 +8001,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>camarasaurus</t>
+          <t>allosaurus</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -8073,27 +8011,27 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>riparovenator</t>
+          <t>camarasaurus</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>lokiceratops</t>
+          <t>amargasaurus</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>brachylophosaurus</t>
+          <t>iguanodon</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -8103,7 +8041,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>huaxiadraco</t>
+          <t>pachycephalosaurus</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -8113,7 +8051,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>diplodocus</t>
+          <t>riparovenator</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -8123,7 +8061,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>apatosaurus</t>
+          <t>lokiceratops</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -8133,7 +8071,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>torvosaurus</t>
+          <t>huaxiadraco</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -8143,7 +8081,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>tyrannotitan</t>
+          <t>brachylophosaurus</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -8153,37 +8091,37 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>gregarismo</t>
+          <t>diplodocus</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>trampa</t>
+          <t>apatosaurus</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>rebrote</t>
+          <t>tyrannotitan</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>gastrolitos</t>
+          <t>gregarismo</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
@@ -8193,7 +8131,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>fractura</t>
+          <t>trampa</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
@@ -8203,57 +8141,57 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>sabana</t>
+          <t>rebrote</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>aridez</t>
+          <t>nido</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>canal</t>
+          <t>sabana_helechos</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>mortandad</t>
+          <t>insectos</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>crecimiento_acelerado</t>
+          <t>fractura</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>neumaticidad</t>
+          <t>gastrolitos</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
@@ -8263,7 +8201,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>competencia</t>
+          <t>crecimiento_acelerado</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
@@ -8273,11 +8211,51 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>sabana</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>canal_trenzado</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>biomasa</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>7</v>
+      <c r="B34" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>araucarias</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>cicadas</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
